--- a/docs/gantt-chart.xlsx
+++ b/docs/gantt-chart.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rakul/Desktop/cs/4sem/researchproj/foodscraper/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EE094DC6-BA5F-7E4E-BB89-8816383DF8C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29EEF6F9-7B9C-4248-A0DE-C4ADC085DEDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -113,9 +113,6 @@
     <t>Initiation</t>
   </si>
   <si>
-    <t>Planning and design</t>
-  </si>
-  <si>
     <t>Project start:</t>
   </si>
   <si>
@@ -180,6 +177,9 @@
   </si>
   <si>
     <t>Supervisor: Vedran Sekara</t>
+  </si>
+  <si>
+    <t>Planning and knowledge gaining</t>
   </si>
 </sst>
 </file>
@@ -814,7 +814,7 @@
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -994,6 +994,85 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="15" fillId="3" borderId="6" xfId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="15" fillId="3" borderId="7" xfId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="15" fillId="4" borderId="5" xfId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="15" fillId="5" borderId="8" xfId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="15" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="15" fillId="10" borderId="9" xfId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="9" xfId="11" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="14" fontId="16" fillId="10" borderId="9" xfId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="15" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="15" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="15" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="23" fillId="0" borderId="0" xfId="8" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="7" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1002,88 +1081,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="7" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="167" fontId="15" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="15" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="15" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="23" fillId="0" borderId="0" xfId="8" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="15" fillId="3" borderId="6" xfId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="15" fillId="3" borderId="7" xfId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="15" fillId="4" borderId="5" xfId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="15" fillId="5" borderId="8" xfId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="15" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="15" fillId="10" borderId="9" xfId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="9" xfId="11" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="14" fontId="16" fillId="10" borderId="9" xfId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="12">
@@ -1100,7 +1097,18 @@
     <cellStyle name="Title" xfId="4" builtinId="15" customBuiltin="1"/>
     <cellStyle name="zHiddenText" xfId="2" xr:uid="{26E66EE6-E33F-4D77-BAE4-0FB4F5BBF673}"/>
   </cellStyles>
-  <dxfs count="74">
+  <dxfs count="23">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left/>
+        <right/>
+      </border>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1115,18 +1123,41 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="8" tint="0.59996337778862885"/>
+          <bgColor theme="6" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
       <border>
         <left/>
         <right/>
+        <top style="thin">
+          <color theme="0" tint="-4.9989318521683403E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-4.9989318521683403E-2"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="6" tint="0.39994506668294322"/>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="0" tint="-4.9989318521683403E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-4.9989318521683403E-2"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
       <border>
@@ -1158,43 +1189,9 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor theme="5" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </bottom>
-      </border>
     </dxf>
     <dxf>
       <fill>
@@ -1212,14 +1209,15 @@
       </border>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8"/>
-        </patternFill>
-      </fill>
       <border>
-        <left/>
-        <right/>
+        <left style="thin">
+          <color theme="5"/>
+        </left>
+        <right style="thin">
+          <color theme="5"/>
+        </right>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -1236,27 +1234,23 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="8"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left/>
+        <right/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="6" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
       <border>
         <left/>
         <right/>
-        <top style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border>
         <top style="thin">
           <color theme="0" tint="-4.9989318521683403E-2"/>
         </top>
@@ -1285,13 +1279,6 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor theme="4" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
@@ -1304,693 +1291,6 @@
         <bottom style="thin">
           <color theme="0" tint="-4.9989318521683403E-2"/>
         </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color theme="5"/>
-        </left>
-        <right style="thin">
-          <color theme="5"/>
-        </right>
-        <vertical/>
-        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -2089,15 +1389,15 @@
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="ToDoList" pivot="0" count="9" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" dxfId="73"/>
-      <tableStyleElement type="headerRow" dxfId="72"/>
-      <tableStyleElement type="totalRow" dxfId="71"/>
-      <tableStyleElement type="firstColumn" dxfId="70"/>
-      <tableStyleElement type="lastColumn" dxfId="69"/>
-      <tableStyleElement type="firstRowStripe" dxfId="68"/>
-      <tableStyleElement type="secondRowStripe" dxfId="67"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="66"/>
-      <tableStyleElement type="secondColumnStripe" dxfId="65"/>
+      <tableStyleElement type="wholeTable" dxfId="22"/>
+      <tableStyleElement type="headerRow" dxfId="21"/>
+      <tableStyleElement type="totalRow" dxfId="20"/>
+      <tableStyleElement type="firstColumn" dxfId="19"/>
+      <tableStyleElement type="lastColumn" dxfId="18"/>
+      <tableStyleElement type="firstRowStripe" dxfId="17"/>
+      <tableStyleElement type="secondRowStripe" dxfId="16"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="15"/>
+      <tableStyleElement type="secondColumnStripe" dxfId="14"/>
     </tableStyle>
   </tableStyles>
   <colors>
@@ -2466,239 +1766,239 @@
   <sheetData>
     <row r="1" spans="1:111" ht="138" customHeight="1" x14ac:dyDescent="0.85">
       <c r="A1" s="13"/>
-      <c r="B1" s="94" t="s">
-        <v>39</v>
+      <c r="B1" s="79" t="s">
+        <v>38</v>
       </c>
       <c r="C1" s="16"/>
       <c r="D1" s="17"/>
       <c r="F1" s="1"/>
-      <c r="G1" s="72" t="s">
-        <v>21</v>
-      </c>
-      <c r="H1" s="73"/>
-      <c r="I1" s="73"/>
-      <c r="J1" s="73"/>
-      <c r="K1" s="73"/>
-      <c r="L1" s="73"/>
-      <c r="M1" s="73"/>
+      <c r="G1" s="92" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1" s="93"/>
+      <c r="I1" s="93"/>
+      <c r="J1" s="93"/>
+      <c r="K1" s="93"/>
+      <c r="L1" s="93"/>
+      <c r="M1" s="93"/>
       <c r="N1" s="20"/>
-      <c r="O1" s="77">
+      <c r="O1" s="90">
         <v>46062</v>
       </c>
-      <c r="P1" s="78"/>
-      <c r="Q1" s="78"/>
-      <c r="R1" s="78"/>
-      <c r="S1" s="78"/>
-      <c r="T1" s="78"/>
-      <c r="U1" s="78"/>
-      <c r="V1" s="78"/>
-      <c r="W1" s="78"/>
-      <c r="X1" s="78"/>
+      <c r="P1" s="91"/>
+      <c r="Q1" s="91"/>
+      <c r="R1" s="91"/>
+      <c r="S1" s="91"/>
+      <c r="T1" s="91"/>
+      <c r="U1" s="91"/>
+      <c r="V1" s="91"/>
+      <c r="W1" s="91"/>
+      <c r="X1" s="91"/>
     </row>
     <row r="2" spans="1:111" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="57" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C2" s="19"/>
       <c r="D2" s="18"/>
-      <c r="G2" s="72" t="s">
-        <v>22</v>
-      </c>
-      <c r="H2" s="73"/>
-      <c r="I2" s="73"/>
-      <c r="J2" s="73"/>
-      <c r="K2" s="73"/>
-      <c r="L2" s="73"/>
-      <c r="M2" s="73"/>
+      <c r="G2" s="92" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2" s="93"/>
+      <c r="I2" s="93"/>
+      <c r="J2" s="93"/>
+      <c r="K2" s="93"/>
+      <c r="L2" s="93"/>
+      <c r="M2" s="93"/>
       <c r="N2" s="20"/>
-      <c r="O2" s="70">
+      <c r="O2" s="88">
         <v>1</v>
       </c>
-      <c r="P2" s="71"/>
-      <c r="Q2" s="71"/>
-      <c r="R2" s="71"/>
-      <c r="S2" s="71"/>
-      <c r="T2" s="71"/>
-      <c r="U2" s="71"/>
-      <c r="V2" s="71"/>
-      <c r="W2" s="71"/>
-      <c r="X2" s="71"/>
+      <c r="P2" s="89"/>
+      <c r="Q2" s="89"/>
+      <c r="R2" s="89"/>
+      <c r="S2" s="89"/>
+      <c r="T2" s="89"/>
+      <c r="U2" s="89"/>
+      <c r="V2" s="89"/>
+      <c r="W2" s="89"/>
+      <c r="X2" s="89"/>
     </row>
     <row r="3" spans="1:111" s="21" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="12"/>
-      <c r="B3" s="96" t="s">
-        <v>41</v>
-      </c>
-      <c r="C3" s="95"/>
-      <c r="D3" s="95"/>
+      <c r="B3" s="81" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" s="80"/>
+      <c r="D3" s="80"/>
     </row>
     <row r="4" spans="1:111" s="21" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="13"/>
-      <c r="B4" s="97" t="s">
-        <v>42</v>
-      </c>
-      <c r="C4" s="95"/>
-      <c r="D4" s="95"/>
-      <c r="G4" s="76">
+      <c r="B4" s="82" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" s="80"/>
+      <c r="D4" s="80"/>
+      <c r="G4" s="85">
         <f>G5</f>
         <v>46062</v>
       </c>
-      <c r="H4" s="74"/>
-      <c r="I4" s="74"/>
-      <c r="J4" s="74"/>
-      <c r="K4" s="74"/>
-      <c r="L4" s="74"/>
-      <c r="M4" s="74"/>
-      <c r="N4" s="74">
+      <c r="H4" s="83"/>
+      <c r="I4" s="83"/>
+      <c r="J4" s="83"/>
+      <c r="K4" s="83"/>
+      <c r="L4" s="83"/>
+      <c r="M4" s="83"/>
+      <c r="N4" s="83">
         <f>N5</f>
         <v>46069</v>
       </c>
-      <c r="O4" s="74"/>
-      <c r="P4" s="74"/>
-      <c r="Q4" s="74"/>
-      <c r="R4" s="74"/>
-      <c r="S4" s="74"/>
-      <c r="T4" s="74"/>
-      <c r="U4" s="74">
+      <c r="O4" s="83"/>
+      <c r="P4" s="83"/>
+      <c r="Q4" s="83"/>
+      <c r="R4" s="83"/>
+      <c r="S4" s="83"/>
+      <c r="T4" s="83"/>
+      <c r="U4" s="83">
         <f>U5</f>
         <v>46076</v>
       </c>
-      <c r="V4" s="74"/>
-      <c r="W4" s="74"/>
-      <c r="X4" s="74"/>
-      <c r="Y4" s="74"/>
-      <c r="Z4" s="74"/>
-      <c r="AA4" s="74"/>
-      <c r="AB4" s="74">
+      <c r="V4" s="83"/>
+      <c r="W4" s="83"/>
+      <c r="X4" s="83"/>
+      <c r="Y4" s="83"/>
+      <c r="Z4" s="83"/>
+      <c r="AA4" s="83"/>
+      <c r="AB4" s="83">
         <f>AB5</f>
         <v>46083</v>
       </c>
-      <c r="AC4" s="74"/>
-      <c r="AD4" s="74"/>
-      <c r="AE4" s="74"/>
-      <c r="AF4" s="74"/>
-      <c r="AG4" s="74"/>
-      <c r="AH4" s="74"/>
-      <c r="AI4" s="74">
+      <c r="AC4" s="83"/>
+      <c r="AD4" s="83"/>
+      <c r="AE4" s="83"/>
+      <c r="AF4" s="83"/>
+      <c r="AG4" s="83"/>
+      <c r="AH4" s="83"/>
+      <c r="AI4" s="83">
         <f>AI5</f>
         <v>46090</v>
       </c>
-      <c r="AJ4" s="74"/>
-      <c r="AK4" s="74"/>
-      <c r="AL4" s="74"/>
-      <c r="AM4" s="74"/>
-      <c r="AN4" s="74"/>
-      <c r="AO4" s="74"/>
-      <c r="AP4" s="74">
+      <c r="AJ4" s="83"/>
+      <c r="AK4" s="83"/>
+      <c r="AL4" s="83"/>
+      <c r="AM4" s="83"/>
+      <c r="AN4" s="83"/>
+      <c r="AO4" s="83"/>
+      <c r="AP4" s="83">
         <f>AP5</f>
         <v>46097</v>
       </c>
-      <c r="AQ4" s="74"/>
-      <c r="AR4" s="74"/>
-      <c r="AS4" s="74"/>
-      <c r="AT4" s="74"/>
-      <c r="AU4" s="74"/>
-      <c r="AV4" s="74"/>
-      <c r="AW4" s="74">
+      <c r="AQ4" s="83"/>
+      <c r="AR4" s="83"/>
+      <c r="AS4" s="83"/>
+      <c r="AT4" s="83"/>
+      <c r="AU4" s="83"/>
+      <c r="AV4" s="83"/>
+      <c r="AW4" s="83">
         <f>AW5</f>
         <v>46104</v>
       </c>
-      <c r="AX4" s="74"/>
-      <c r="AY4" s="74"/>
-      <c r="AZ4" s="74"/>
-      <c r="BA4" s="74"/>
-      <c r="BB4" s="74"/>
-      <c r="BC4" s="74"/>
-      <c r="BD4" s="74">
+      <c r="AX4" s="83"/>
+      <c r="AY4" s="83"/>
+      <c r="AZ4" s="83"/>
+      <c r="BA4" s="83"/>
+      <c r="BB4" s="83"/>
+      <c r="BC4" s="83"/>
+      <c r="BD4" s="83">
         <f>BD5</f>
         <v>46111</v>
       </c>
-      <c r="BE4" s="74"/>
-      <c r="BF4" s="74"/>
-      <c r="BG4" s="74"/>
-      <c r="BH4" s="74"/>
-      <c r="BI4" s="74"/>
-      <c r="BJ4" s="75"/>
-      <c r="BK4" s="74">
+      <c r="BE4" s="83"/>
+      <c r="BF4" s="83"/>
+      <c r="BG4" s="83"/>
+      <c r="BH4" s="83"/>
+      <c r="BI4" s="83"/>
+      <c r="BJ4" s="84"/>
+      <c r="BK4" s="83">
         <f>BK5</f>
         <v>46118</v>
       </c>
-      <c r="BL4" s="74"/>
-      <c r="BM4" s="74"/>
-      <c r="BN4" s="74"/>
-      <c r="BO4" s="74"/>
-      <c r="BP4" s="74"/>
-      <c r="BQ4" s="75"/>
-      <c r="BR4" s="74">
+      <c r="BL4" s="83"/>
+      <c r="BM4" s="83"/>
+      <c r="BN4" s="83"/>
+      <c r="BO4" s="83"/>
+      <c r="BP4" s="83"/>
+      <c r="BQ4" s="84"/>
+      <c r="BR4" s="83">
         <f>BR5</f>
         <v>46125</v>
       </c>
-      <c r="BS4" s="74"/>
-      <c r="BT4" s="74"/>
-      <c r="BU4" s="74"/>
-      <c r="BV4" s="74"/>
-      <c r="BW4" s="74"/>
-      <c r="BX4" s="75"/>
-      <c r="BY4" s="74">
+      <c r="BS4" s="83"/>
+      <c r="BT4" s="83"/>
+      <c r="BU4" s="83"/>
+      <c r="BV4" s="83"/>
+      <c r="BW4" s="83"/>
+      <c r="BX4" s="84"/>
+      <c r="BY4" s="83">
         <f>BY5</f>
         <v>46132</v>
       </c>
-      <c r="BZ4" s="74"/>
-      <c r="CA4" s="74"/>
-      <c r="CB4" s="74"/>
-      <c r="CC4" s="74"/>
-      <c r="CD4" s="74"/>
-      <c r="CE4" s="75"/>
-      <c r="CF4" s="74">
+      <c r="BZ4" s="83"/>
+      <c r="CA4" s="83"/>
+      <c r="CB4" s="83"/>
+      <c r="CC4" s="83"/>
+      <c r="CD4" s="83"/>
+      <c r="CE4" s="84"/>
+      <c r="CF4" s="83">
         <f>CF5</f>
         <v>46139</v>
       </c>
-      <c r="CG4" s="74"/>
-      <c r="CH4" s="74"/>
-      <c r="CI4" s="74"/>
-      <c r="CJ4" s="74"/>
-      <c r="CK4" s="74"/>
-      <c r="CL4" s="75"/>
-      <c r="CM4" s="74">
+      <c r="CG4" s="83"/>
+      <c r="CH4" s="83"/>
+      <c r="CI4" s="83"/>
+      <c r="CJ4" s="83"/>
+      <c r="CK4" s="83"/>
+      <c r="CL4" s="84"/>
+      <c r="CM4" s="83">
         <f>CM5</f>
         <v>46146</v>
       </c>
-      <c r="CN4" s="74"/>
-      <c r="CO4" s="74"/>
-      <c r="CP4" s="74"/>
-      <c r="CQ4" s="74"/>
-      <c r="CR4" s="74"/>
-      <c r="CS4" s="75"/>
-      <c r="CT4" s="74">
+      <c r="CN4" s="83"/>
+      <c r="CO4" s="83"/>
+      <c r="CP4" s="83"/>
+      <c r="CQ4" s="83"/>
+      <c r="CR4" s="83"/>
+      <c r="CS4" s="84"/>
+      <c r="CT4" s="83">
         <f>CT5</f>
         <v>46153</v>
       </c>
-      <c r="CU4" s="74"/>
-      <c r="CV4" s="74"/>
-      <c r="CW4" s="74"/>
-      <c r="CX4" s="74"/>
-      <c r="CY4" s="74"/>
-      <c r="CZ4" s="75"/>
-      <c r="DA4" s="74">
+      <c r="CU4" s="83"/>
+      <c r="CV4" s="83"/>
+      <c r="CW4" s="83"/>
+      <c r="CX4" s="83"/>
+      <c r="CY4" s="83"/>
+      <c r="CZ4" s="84"/>
+      <c r="DA4" s="83">
         <f>DA5</f>
         <v>46160</v>
       </c>
-      <c r="DB4" s="74"/>
-      <c r="DC4" s="74"/>
-      <c r="DD4" s="74"/>
-      <c r="DE4" s="74"/>
-      <c r="DF4" s="74"/>
-      <c r="DG4" s="75"/>
+      <c r="DB4" s="83"/>
+      <c r="DC4" s="83"/>
+      <c r="DD4" s="83"/>
+      <c r="DE4" s="83"/>
+      <c r="DF4" s="83"/>
+      <c r="DG4" s="84"/>
     </row>
     <row r="5" spans="1:111" s="21" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="65"/>
-      <c r="B5" s="66" t="s">
+      <c r="A5" s="94"/>
+      <c r="B5" s="95" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="69" t="s">
+      <c r="C5" s="86" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="69" t="s">
+      <c r="D5" s="86" t="s">
         <v>3</v>
       </c>
       <c r="G5" s="22">
@@ -3123,10 +2423,10 @@
       </c>
     </row>
     <row r="6" spans="1:111" s="21" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="65"/>
-      <c r="B6" s="67"/>
-      <c r="C6" s="68"/>
-      <c r="D6" s="68"/>
+      <c r="A6" s="94"/>
+      <c r="B6" s="96"/>
+      <c r="C6" s="87"/>
+      <c r="D6" s="87"/>
       <c r="G6" s="25" t="str">
         <f t="shared" ref="G6:AL6" si="38">LEFT(TEXT(G5,"ddd"),1)</f>
         <v>M</v>
@@ -3786,13 +3086,13 @@
     <row r="9" spans="1:111" s="34" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A9" s="13"/>
       <c r="B9" s="35" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" s="83">
+        <v>23</v>
+      </c>
+      <c r="C9" s="69">
         <f>Project_Start</f>
         <v>46062</v>
       </c>
-      <c r="D9" s="83">
+      <c r="D9" s="69">
         <f>C9+6</f>
         <v>46068</v>
       </c>
@@ -3910,13 +3210,13 @@
     <row r="10" spans="1:111" s="34" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A10" s="13"/>
       <c r="B10" s="37" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" s="84">
+        <v>24</v>
+      </c>
+      <c r="C10" s="70">
         <f>D9+1</f>
         <v>46069</v>
       </c>
-      <c r="D10" s="84">
+      <c r="D10" s="70">
         <f>C10+6</f>
         <v>46075</v>
       </c>
@@ -3936,7 +3236,7 @@
       <c r="O10" s="36"/>
       <c r="P10" s="36"/>
       <c r="Q10" s="36"/>
-      <c r="R10" s="81"/>
+      <c r="R10" s="67"/>
       <c r="S10" s="38"/>
       <c r="T10" s="38"/>
       <c r="U10" s="36"/>
@@ -4034,12 +3334,12 @@
     <row r="11" spans="1:111" s="34" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A11" s="12"/>
       <c r="B11" s="37" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" s="84">
+        <v>29</v>
+      </c>
+      <c r="C11" s="70">
         <v>46073</v>
       </c>
-      <c r="D11" s="84">
+      <c r="D11" s="70">
         <f>C11</f>
         <v>46073</v>
       </c>
@@ -4058,9 +3358,9 @@
       <c r="N11" s="36"/>
       <c r="O11" s="36"/>
       <c r="P11" s="36"/>
-      <c r="Q11" s="79"/>
-      <c r="R11" s="82"/>
-      <c r="S11" s="80"/>
+      <c r="Q11" s="65"/>
+      <c r="R11" s="68"/>
+      <c r="S11" s="66"/>
       <c r="T11" s="36"/>
       <c r="U11" s="36"/>
       <c r="V11" s="36"/>
@@ -4157,7 +3457,7 @@
     <row r="12" spans="1:111" s="34" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A12" s="13"/>
       <c r="B12" s="39" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="C12" s="40"/>
       <c r="D12" s="41"/>
@@ -4170,13 +3470,13 @@
     <row r="13" spans="1:111" s="34" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A13" s="13"/>
       <c r="B13" s="42" t="s">
-        <v>26</v>
-      </c>
-      <c r="C13" s="85">
+        <v>25</v>
+      </c>
+      <c r="C13" s="71">
         <f>D11+3</f>
         <v>46076</v>
       </c>
-      <c r="D13" s="85">
+      <c r="D13" s="71">
         <f>C13+6</f>
         <v>46082</v>
       </c>
@@ -4294,13 +3594,13 @@
     <row r="14" spans="1:111" s="34" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A14" s="12"/>
       <c r="B14" s="42" t="s">
-        <v>27</v>
-      </c>
-      <c r="C14" s="85">
+        <v>26</v>
+      </c>
+      <c r="C14" s="71">
         <f>D13+1</f>
         <v>46083</v>
       </c>
-      <c r="D14" s="85">
+      <c r="D14" s="71">
         <f>C14+13</f>
         <v>46096</v>
       </c>
@@ -4418,13 +3718,13 @@
     <row r="15" spans="1:111" s="34" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A15" s="12"/>
       <c r="B15" s="42" t="s">
-        <v>28</v>
-      </c>
-      <c r="C15" s="85">
+        <v>27</v>
+      </c>
+      <c r="C15" s="71">
         <f>D14+1</f>
         <v>46097</v>
       </c>
-      <c r="D15" s="85">
+      <c r="D15" s="71">
         <f>C15+6</f>
         <v>46103</v>
       </c>
@@ -4542,7 +3842,7 @@
     <row r="16" spans="1:111" s="34" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A16" s="12"/>
       <c r="B16" s="43" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C16" s="44"/>
       <c r="D16" s="45"/>
@@ -4660,13 +3960,13 @@
     <row r="17" spans="1:111" s="34" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A17" s="12"/>
       <c r="B17" s="47" t="s">
-        <v>32</v>
-      </c>
-      <c r="C17" s="86">
+        <v>31</v>
+      </c>
+      <c r="C17" s="72">
         <f>D15+1</f>
         <v>46104</v>
       </c>
-      <c r="D17" s="86">
+      <c r="D17" s="72">
         <f>C17+21</f>
         <v>46125</v>
       </c>
@@ -4784,13 +4084,13 @@
     <row r="18" spans="1:111" s="34" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A18" s="12"/>
       <c r="B18" s="47" t="s">
-        <v>33</v>
-      </c>
-      <c r="C18" s="86">
+        <v>32</v>
+      </c>
+      <c r="C18" s="72">
         <f>C17</f>
         <v>46104</v>
       </c>
-      <c r="D18" s="86">
+      <c r="D18" s="72">
         <f>C18+21</f>
         <v>46125</v>
       </c>
@@ -4908,13 +4208,13 @@
     <row r="19" spans="1:111" s="34" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12"/>
       <c r="B19" s="47" t="s">
-        <v>38</v>
-      </c>
-      <c r="C19" s="86">
+        <v>37</v>
+      </c>
+      <c r="C19" s="72">
         <f>C18+7</f>
         <v>46111</v>
       </c>
-      <c r="D19" s="86">
+      <c r="D19" s="72">
         <f>C19+21</f>
         <v>46132</v>
       </c>
@@ -5032,10 +4332,10 @@
     <row r="20" spans="1:111" s="34" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A20" s="12"/>
       <c r="B20" s="48" t="s">
-        <v>23</v>
-      </c>
-      <c r="C20" s="87"/>
-      <c r="D20" s="88"/>
+        <v>22</v>
+      </c>
+      <c r="C20" s="73"/>
+      <c r="D20" s="74"/>
       <c r="E20" s="15"/>
       <c r="F20" s="4" t="str">
         <f t="shared" si="41"/>
@@ -5150,13 +4450,13 @@
     <row r="21" spans="1:111" s="34" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A21" s="12"/>
       <c r="B21" s="50" t="s">
-        <v>34</v>
-      </c>
-      <c r="C21" s="89">
+        <v>33</v>
+      </c>
+      <c r="C21" s="75">
         <f>C17+7</f>
         <v>46111</v>
       </c>
-      <c r="D21" s="89">
+      <c r="D21" s="75">
         <f>C21+21</f>
         <v>46132</v>
       </c>
@@ -5274,13 +4574,13 @@
     <row r="22" spans="1:111" s="34" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A22" s="12"/>
       <c r="B22" s="50" t="s">
-        <v>35</v>
-      </c>
-      <c r="C22" s="89">
+        <v>34</v>
+      </c>
+      <c r="C22" s="75">
         <f>D21</f>
         <v>46132</v>
       </c>
-      <c r="D22" s="89">
+      <c r="D22" s="75">
         <f>C22+14</f>
         <v>46146</v>
       </c>
@@ -5398,13 +4698,13 @@
     <row r="23" spans="1:111" s="34" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A23" s="12"/>
       <c r="B23" s="50" t="s">
-        <v>37</v>
-      </c>
-      <c r="C23" s="89">
+        <v>36</v>
+      </c>
+      <c r="C23" s="75">
         <f>D22+1</f>
         <v>46147</v>
       </c>
-      <c r="D23" s="89">
+      <c r="D23" s="75">
         <f>C23</f>
         <v>46147</v>
       </c>
@@ -5522,13 +4822,13 @@
     <row r="24" spans="1:111" s="34" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A24" s="12"/>
       <c r="B24" s="50" t="s">
-        <v>36</v>
-      </c>
-      <c r="C24" s="89">
+        <v>35</v>
+      </c>
+      <c r="C24" s="75">
         <f>D23+1</f>
         <v>46148</v>
       </c>
-      <c r="D24" s="89">
+      <c r="D24" s="75">
         <f>C24+8</f>
         <v>46156</v>
       </c>
@@ -5623,15 +4923,15 @@
       <c r="CL24" s="36"/>
       <c r="CM24" s="36"/>
       <c r="CN24" s="36"/>
-      <c r="CO24" s="91"/>
-      <c r="CP24" s="91"/>
-      <c r="CQ24" s="91"/>
-      <c r="CR24" s="91"/>
-      <c r="CS24" s="91"/>
-      <c r="CT24" s="91"/>
-      <c r="CU24" s="91"/>
-      <c r="CV24" s="90"/>
-      <c r="CW24" s="90"/>
+      <c r="CO24" s="36"/>
+      <c r="CP24" s="36"/>
+      <c r="CQ24" s="36"/>
+      <c r="CR24" s="36"/>
+      <c r="CS24" s="36"/>
+      <c r="CT24" s="36"/>
+      <c r="CU24" s="36"/>
+      <c r="CV24" s="76"/>
+      <c r="CW24" s="76"/>
       <c r="CX24" s="36"/>
       <c r="CY24" s="36"/>
       <c r="CZ24" s="36"/>
@@ -5645,13 +4945,13 @@
     </row>
     <row r="25" spans="1:111" s="34" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A25" s="12"/>
-      <c r="B25" s="92" t="s">
-        <v>29</v>
-      </c>
-      <c r="C25" s="93">
+      <c r="B25" s="77" t="s">
+        <v>28</v>
+      </c>
+      <c r="C25" s="78">
         <v>46157</v>
       </c>
-      <c r="D25" s="93">
+      <c r="D25" s="78">
         <v>46157</v>
       </c>
       <c r="E25" s="15"/>
@@ -6007,13 +5307,14 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="CT4:CZ4"/>
-    <mergeCell ref="DA4:DG4"/>
-    <mergeCell ref="BK4:BQ4"/>
-    <mergeCell ref="BR4:BX4"/>
-    <mergeCell ref="BY4:CE4"/>
-    <mergeCell ref="CF4:CL4"/>
-    <mergeCell ref="CM4:CS4"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="O2:X2"/>
+    <mergeCell ref="O1:X1"/>
+    <mergeCell ref="G1:M1"/>
+    <mergeCell ref="G2:M2"/>
     <mergeCell ref="BD4:BJ4"/>
     <mergeCell ref="G4:M4"/>
     <mergeCell ref="N4:T4"/>
@@ -6022,274 +5323,78 @@
     <mergeCell ref="AI4:AO4"/>
     <mergeCell ref="AP4:AV4"/>
     <mergeCell ref="AW4:BC4"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="O2:X2"/>
-    <mergeCell ref="O1:X1"/>
-    <mergeCell ref="G1:M1"/>
-    <mergeCell ref="G2:M2"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="CT4:CZ4"/>
+    <mergeCell ref="DA4:DG4"/>
+    <mergeCell ref="BK4:BQ4"/>
+    <mergeCell ref="BR4:BX4"/>
+    <mergeCell ref="BY4:CE4"/>
+    <mergeCell ref="CF4:CL4"/>
+    <mergeCell ref="CM4:CS4"/>
   </mergeCells>
-  <conditionalFormatting sqref="G4:DG25">
-    <cfRule type="expression" dxfId="64" priority="64">
-      <formula>AND(TODAY()&gt;=G$5, TODAY()&lt;H$5)</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="G9:BJ11">
-    <cfRule type="expression" dxfId="63" priority="69">
-      <formula>AND(task_start&lt;=G$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=G$5)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="62" priority="70" stopIfTrue="1">
+    <cfRule type="expression" dxfId="13" priority="70" stopIfTrue="1">
       <formula>AND(task_end&gt;=G$5,task_start&lt;H$5)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G13:BJ15">
-    <cfRule type="expression" dxfId="61" priority="67">
-      <formula>AND(task_start&lt;=G$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=G$5)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="60" priority="68" stopIfTrue="1">
+    <cfRule type="expression" dxfId="12" priority="68" stopIfTrue="1">
       <formula>AND(task_end&gt;=G$5,task_start&lt;H$5)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G17:BJ19">
-    <cfRule type="expression" dxfId="59" priority="65">
-      <formula>AND(task_start&lt;=G$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=G$5)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="58" priority="66" stopIfTrue="1">
+    <cfRule type="expression" dxfId="11" priority="66" stopIfTrue="1">
       <formula>AND(task_end&gt;=G$5,task_start&lt;H$5)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G21:BJ25">
-    <cfRule type="expression" dxfId="57" priority="99">
+    <cfRule type="expression" dxfId="10" priority="100" stopIfTrue="1">
+      <formula>AND(task_end&gt;=G$5,task_start&lt;H$5)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="9" priority="99">
       <formula>AND(task_start&lt;=G$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=G$5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="56" priority="100" stopIfTrue="1">
-      <formula>AND(task_end&gt;=G$5,task_start&lt;H$5)</formula>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G4:DG25">
+    <cfRule type="expression" dxfId="8" priority="64">
+      <formula>AND(TODAY()&gt;=G$5, TODAY()&lt;H$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BK9:BQ11">
-    <cfRule type="expression" dxfId="55" priority="60">
-      <formula>AND(task_start&lt;=BK$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=BK$5)</formula>
+  <conditionalFormatting sqref="G9:DG11">
+    <cfRule type="expression" dxfId="7" priority="6">
+      <formula>AND(task_start&lt;=G$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=G$5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="54" priority="61" stopIfTrue="1">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G13:DG15">
+    <cfRule type="expression" dxfId="6" priority="4">
+      <formula>AND(task_start&lt;=G$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=G$5)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G17:DG19">
+    <cfRule type="expression" dxfId="5" priority="2">
+      <formula>AND(task_start&lt;=G$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=G$5)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BK9:DG11">
+    <cfRule type="expression" dxfId="4" priority="7" stopIfTrue="1">
       <formula>AND(task_end&gt;=BK$5,task_start&lt;BL$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BK13:BQ15">
-    <cfRule type="expression" dxfId="53" priority="58">
-      <formula>AND(task_start&lt;=BK$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=BK$5)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="52" priority="59" stopIfTrue="1">
+  <conditionalFormatting sqref="BK13:DG15">
+    <cfRule type="expression" dxfId="3" priority="5" stopIfTrue="1">
       <formula>AND(task_end&gt;=BK$5,task_start&lt;BL$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BK17:BQ19">
-    <cfRule type="expression" dxfId="51" priority="56">
-      <formula>AND(task_start&lt;=BK$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=BK$5)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="50" priority="57" stopIfTrue="1">
+  <conditionalFormatting sqref="BK17:DG19">
+    <cfRule type="expression" dxfId="2" priority="3" stopIfTrue="1">
       <formula>AND(task_end&gt;=BK$5,task_start&lt;BL$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BK21:BQ25">
-    <cfRule type="expression" dxfId="49" priority="62">
-      <formula>AND(task_start&lt;=BK$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=BK$5)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="48" priority="63" stopIfTrue="1">
+  <conditionalFormatting sqref="BK21:DG25">
+    <cfRule type="expression" dxfId="1" priority="9" stopIfTrue="1">
       <formula>AND(task_end&gt;=BK$5,task_start&lt;BL$5)</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="BR9:BX11">
-    <cfRule type="expression" dxfId="47" priority="51">
-      <formula>AND(task_start&lt;=BR$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=BR$5)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="46" priority="52" stopIfTrue="1">
-      <formula>AND(task_end&gt;=BR$5,task_start&lt;BS$5)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="BR13:BX15">
-    <cfRule type="expression" dxfId="45" priority="49">
-      <formula>AND(task_start&lt;=BR$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=BR$5)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="44" priority="50" stopIfTrue="1">
-      <formula>AND(task_end&gt;=BR$5,task_start&lt;BS$5)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="BR17:BX19">
-    <cfRule type="expression" dxfId="43" priority="47">
-      <formula>AND(task_start&lt;=BR$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=BR$5)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="42" priority="48" stopIfTrue="1">
-      <formula>AND(task_end&gt;=BR$5,task_start&lt;BS$5)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="BR21:BX25">
-    <cfRule type="expression" dxfId="41" priority="53">
-      <formula>AND(task_start&lt;=BR$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=BR$5)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="40" priority="54" stopIfTrue="1">
-      <formula>AND(task_end&gt;=BR$5,task_start&lt;BS$5)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="BY9:CE11">
-    <cfRule type="expression" dxfId="39" priority="42">
-      <formula>AND(task_start&lt;=BY$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=BY$5)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="38" priority="43" stopIfTrue="1">
-      <formula>AND(task_end&gt;=BY$5,task_start&lt;BZ$5)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="BY13:CE15">
-    <cfRule type="expression" dxfId="37" priority="40">
-      <formula>AND(task_start&lt;=BY$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=BY$5)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="36" priority="41" stopIfTrue="1">
-      <formula>AND(task_end&gt;=BY$5,task_start&lt;BZ$5)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="BY17:CE19">
-    <cfRule type="expression" dxfId="35" priority="38">
-      <formula>AND(task_start&lt;=BY$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=BY$5)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="34" priority="39" stopIfTrue="1">
-      <formula>AND(task_end&gt;=BY$5,task_start&lt;BZ$5)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="BY21:CE25">
-    <cfRule type="expression" dxfId="33" priority="44">
-      <formula>AND(task_start&lt;=BY$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=BY$5)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="32" priority="45" stopIfTrue="1">
-      <formula>AND(task_end&gt;=BY$5,task_start&lt;BZ$5)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="CF9:CL11">
-    <cfRule type="expression" dxfId="31" priority="33">
-      <formula>AND(task_start&lt;=CF$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=CF$5)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="30" priority="34" stopIfTrue="1">
-      <formula>AND(task_end&gt;=CF$5,task_start&lt;CG$5)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="CF13:CL15">
-    <cfRule type="expression" dxfId="29" priority="31">
-      <formula>AND(task_start&lt;=CF$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=CF$5)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="28" priority="32" stopIfTrue="1">
-      <formula>AND(task_end&gt;=CF$5,task_start&lt;CG$5)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="CF17:CL19">
-    <cfRule type="expression" dxfId="27" priority="29">
-      <formula>AND(task_start&lt;=CF$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=CF$5)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="26" priority="30" stopIfTrue="1">
-      <formula>AND(task_end&gt;=CF$5,task_start&lt;CG$5)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="CF21:CL25">
-    <cfRule type="expression" dxfId="25" priority="35">
-      <formula>AND(task_start&lt;=CF$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=CF$5)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="24" priority="36" stopIfTrue="1">
-      <formula>AND(task_end&gt;=CF$5,task_start&lt;CG$5)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="CM9:CS11">
-    <cfRule type="expression" dxfId="23" priority="24">
-      <formula>AND(task_start&lt;=CM$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=CM$5)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="22" priority="25" stopIfTrue="1">
-      <formula>AND(task_end&gt;=CM$5,task_start&lt;CN$5)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="CM13:CS15">
-    <cfRule type="expression" dxfId="21" priority="22">
-      <formula>AND(task_start&lt;=CM$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=CM$5)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="20" priority="23" stopIfTrue="1">
-      <formula>AND(task_end&gt;=CM$5,task_start&lt;CN$5)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="CM17:CS19">
-    <cfRule type="expression" dxfId="19" priority="20">
-      <formula>AND(task_start&lt;=CM$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=CM$5)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="18" priority="21" stopIfTrue="1">
-      <formula>AND(task_end&gt;=CM$5,task_start&lt;CN$5)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="CM21:CS25">
-    <cfRule type="expression" dxfId="17" priority="26">
-      <formula>AND(task_start&lt;=CM$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=CM$5)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="16" priority="27" stopIfTrue="1">
-      <formula>AND(task_end&gt;=CM$5,task_start&lt;CN$5)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="CT9:CZ11">
-    <cfRule type="expression" dxfId="15" priority="15">
-      <formula>AND(task_start&lt;=CT$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=CT$5)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="14" priority="16" stopIfTrue="1">
-      <formula>AND(task_end&gt;=CT$5,task_start&lt;CU$5)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="CT13:CZ15">
-    <cfRule type="expression" dxfId="13" priority="13">
-      <formula>AND(task_start&lt;=CT$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=CT$5)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="12" priority="14" stopIfTrue="1">
-      <formula>AND(task_end&gt;=CT$5,task_start&lt;CU$5)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="CT17:CZ19">
-    <cfRule type="expression" dxfId="11" priority="11">
-      <formula>AND(task_start&lt;=CT$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=CT$5)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="10" priority="12" stopIfTrue="1">
-      <formula>AND(task_end&gt;=CT$5,task_start&lt;CU$5)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="CT21:CZ25">
-    <cfRule type="expression" dxfId="9" priority="17">
-      <formula>AND(task_start&lt;=CT$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=CT$5)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="8" priority="18" stopIfTrue="1">
-      <formula>AND(task_end&gt;=CT$5,task_start&lt;CU$5)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="DA9:DG11">
-    <cfRule type="expression" dxfId="7" priority="6">
-      <formula>AND(task_start&lt;=DA$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=DA$5)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="6" priority="7" stopIfTrue="1">
-      <formula>AND(task_end&gt;=DA$5,task_start&lt;DB$5)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="DA13:DG15">
-    <cfRule type="expression" dxfId="5" priority="4">
-      <formula>AND(task_start&lt;=DA$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=DA$5)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="4" priority="5" stopIfTrue="1">
-      <formula>AND(task_end&gt;=DA$5,task_start&lt;DB$5)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="DA17:DG19">
-    <cfRule type="expression" dxfId="3" priority="2">
-      <formula>AND(task_start&lt;=DA$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=DA$5)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="2" priority="3" stopIfTrue="1">
-      <formula>AND(task_end&gt;=DA$5,task_start&lt;DB$5)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="DA21:DG25">
-    <cfRule type="expression" dxfId="1" priority="8">
-      <formula>AND(task_start&lt;=DA$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=DA$5)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="0" priority="9" stopIfTrue="1">
-      <formula>AND(task_end&gt;=DA$5,task_start&lt;DB$5)</formula>
+    <cfRule type="expression" dxfId="0" priority="8">
+      <formula>AND(task_start&lt;=BK$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=BK$5)</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations disablePrompts="1" count="13">
@@ -6460,15 +5565,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010079F111ED35F8CC479449609E8A0923A6" ma:contentTypeVersion="28" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="60f5a4f2d2b0abadcf532d48ebf9cb71">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xmlns:ns3="16c05727-aa75-4e4a-9b5f-8a80a1165891" xmlns:ns4="230e9df3-be65-4c73-a93b-d1236ebd677e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7dd78129e6a1811f84807ad11c651531" ns1:_="" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -6780,6 +5876,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A82239A0-E68C-493F-BEE6-C77FEA397FD6}">
   <ds:schemaRefs>
@@ -6800,14 +5905,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97245281-08F3-4104-84BD-39F3D8CFB195}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A09426A3-87E9-4865-8A6C-3456B026AE03}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6828,6 +5925,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97245281-08F3-4104-84BD-39F3D8CFB195}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata"/>
 </file>